--- a/processed_ruby_restored_xlsx/sc225_瑠璃７：天体観測.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc225_瑠璃７：天体観測.ss.xlsx
@@ -757,8 +757,8 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>「Nuu... Oji-sama. Mee... desu waah, nuu, suu... suu...
-fuu...」</t>
+          <t>「Nuu... Oji-sama. Mee... desu waah, nuu, suu...
+suu... fuu...」</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1429,8 +1429,8 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>While I touch her butt, she starts grinding her thighs
-together.</t>
+          <t>While I touch her butt, she starts grinding her
+thighs together.</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2012,8 +2012,8 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>She went along with what I said and kept quiet, but if
-I’m right there when she wakes up, of course she’s
+          <t>She went along with what I said and kept quiet, but
+if I’m right there when she wakes up, of course she’s
 going to be curious...</t>
         </is>
       </c>
@@ -2521,7 +2521,8 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>「Th-that's... um, it's a little hard for me to say...」</t>
+          <t>「Th-that's... um, it's a little hard for me to
+say...」</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2582,8 +2583,8 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>「By the way... you were calling my name in your sleep,
-weren't you？」</t>
+          <t>「By the way... you were calling my name in your
+sleep, weren't you？」</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2688,8 +2689,9 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>When I told her to keep her voice down, Rurichiyo-chan
-covered her mouth with both hands again.</t>
+          <t>When I told her to keep her voice down,
+Rurichiyo-chan covered her mouth with both hands
+again.</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2704,8 +2706,8 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>But as if remembering something, she wriggled her hips
-and body a little.</t>
+          <t>But as if remembering something, she wriggled her
+hips and body a little.</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2888,9 +2890,9 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>I was apologizing like that in my head, but being told
-I actually had such a dream surprised me all over
-again.</t>
+          <t>I was apologizing like that in my head, but being
+told I actually had such a dream surprised me all
+over again.</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -3151,8 +3153,8 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>Ghehehehe... I tried imagining that sort of thing, but
-Rurichiyo-chan is actually genuinely scared.</t>
+          <t>Ghehehehe... I tried imagining that sort of thing,
+but Rurichiyo-chan is actually genuinely scared.</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3243,8 +3245,8 @@
       <c r="B182" s="1" t="inlineStr">
         <is>
           <t>Trying to get away from me, Rurichiyo-chan lost her
-balance and unintentionally ended up sticking her butt
-out.</t>
+balance and unintentionally ended up sticking her
+butt out.</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3536,8 +3538,8 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>「...But you're excited about it too, Rurichiyo-chan...
-see...?」</t>
+          <t>「...But you're excited about it too,
+Rurichiyo-chan... see...?」</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3829,8 +3831,8 @@
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t>Saying that, I pulled down my underwear and exposed my
-erect penis.</t>
+          <t>Saying that, I pulled down my underwear and exposed
+my erect penis.</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3875,8 +3877,8 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan twisted around to face me and, spotting
-the penis, her eyes went wide.</t>
+          <t>Rurichiyo-chan twisted around to face me and,
+spotting the penis, her eyes went wide.</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3921,8 +3923,8 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, flustered, kept looking back and forth
-between my face and my penis.</t>
+          <t>Rurichiyo-chan, flustered, kept looking back and
+forth between my face and my penis.</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -4151,8 +4153,8 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>Even though I felt a real response, being refused made
-me let out a truly pathetic sound.</t>
+          <t>Even though I felt a real response, being refused
+made me let out a truly pathetic sound.</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -5433,8 +5435,8 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>Her inside was already soaking wet, wrapping around my
-penis, and just being in felt so good...！</t>
+          <t>Her inside was already soaking wet, wrapping around
+my penis, and just being in felt so good...！</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5495,8 +5497,8 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>「Ah... sorry, I'm really sorry...！ But I just couldn't
-hold back...」</t>
+          <t>「Ah... sorry, I'm really sorry...！ But I just
+couldn't hold back...」</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5511,8 +5513,8 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>...It was here I first realized I'd rushed ahead and I
-panicked and apologized.</t>
+          <t>...It was here I first realized I'd rushed ahead and
+I panicked and apologized.</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5557,8 +5559,9 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>I knew she'd told me no, and since we'd done it anyway
-I might get scolded or, worse, she might hate me.</t>
+          <t>I knew she'd told me no, and since we'd done it
+anyway I might get scolded or, worse, she might hate
+me.</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -5832,7 +5835,8 @@
       </c>
       <c r="B351" s="1" t="inlineStr">
         <is>
-          <t>「Oh... so you really don't intend to stop, do you...？」</t>
+          <t>「Oh... so you really don't intend to stop, do
+you...？」</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -6057,8 +6061,8 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>When I hurriedly said that, she clamped her mouth shut
-this time and breathed out roughly.</t>
+          <t>When I hurriedly said that, she clamped her mouth
+shut this time and breathed out roughly.</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -6165,8 +6169,8 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t>I watch Rurichiyo-chan's reactions as I gently rock my
-hips.</t>
+          <t>I watch Rurichiyo-chan's reactions as I gently rock
+my hips.</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -7186,8 +7190,8 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>I egg Rurichiyo-chan on by praising her, but she might
-be closer to her limit than I thought.</t>
+          <t>I egg Rurichiyo-chan on by praising her, but she
+might be closer to her limit than I thought.</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -7232,8 +7236,8 @@
       </c>
       <c r="B442" s="1" t="inlineStr">
         <is>
-          <t>「Fuh, fuh—ah, nn！ Gotta hold it… nnnah！ Nnaaah… gotta,
-nnaa… haaah…」</t>
+          <t>「Fuh, fuh—ah, nn！ Gotta hold it… nnnah！ Nnaaah…
+gotta, nnaa… haaah…」</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -7263,8 +7267,8 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t>By telling herself that, she's somehow managing not to
-make a sound.</t>
+          <t>By telling herself that, she's somehow managing not
+to make a sound.</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7553,8 +7557,8 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>The sudden stimulation must have caught her off guard,
-and Rurichiyo-chan let out an airy cry.</t>
+          <t>The sudden stimulation must have caught her off
+guard, and Rurichiyo-chan let out an airy cry.</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7814,8 +7818,8 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t>Her pussy has already completely loosened and seems to
-have gotten used to the penis.</t>
+          <t>Her pussy has already completely loosened and seems
+to have gotten used to the penis.</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -7891,8 +7895,8 @@
       </c>
       <c r="B485" s="1" t="inlineStr">
         <is>
-          <t>「Haa, haa... uuu... nn! O-ojii-sama... I can't... make
-it... ahh...!」</t>
+          <t>「Haa, haa... uuu... nn! O-ojii-sama... I can't...
+make it... ahh...!」</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -7922,8 +7926,8 @@
       </c>
       <c r="B487" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nn！ Your voice is getting loud, you know？ Ah...
-I wonder if you noticed？」</t>
+          <t>「Nn... nn！ Your voice is getting loud, you know？
+Ah... I wonder if you noticed？」</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -7953,7 +7957,8 @@
       </c>
       <c r="B489" s="1" t="inlineStr">
         <is>
-          <t>But the volume of our voices might be a trivial thing.</t>
+          <t>But the volume of our voices might be a trivial
+thing.</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -8076,8 +8081,8 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>「Fufu... Rurichiyo-chan？ It seems like Nono-chan might
-wake up, you know？」</t>
+          <t>「Fufu... Rurichiyo-chan？ It seems like Nono-chan
+might wake up, you know？」</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -8277,8 +8282,8 @@
       </c>
       <c r="B510" s="1" t="inlineStr">
         <is>
-          <t>She must have started to buck her hips herself, trying
-to feel me more.</t>
+          <t>She must have started to buck her hips herself,
+trying to feel me more.</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -8400,8 +8405,8 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>I can feel we're joined at the very deepest place, and
-my penis shudders in delight.</t>
+          <t>I can feel we're joined at the very deepest place,
+and my penis shudders in delight.</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8493,8 +8498,8 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan’s voice, her body... and the feeling of
-her pussy — my head was melting into goo.</t>
+          <t>Rurichiyo-chan’s voice, her body... and the feeling
+of her pussy — my head was melting into goo.</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -8540,8 +8545,8 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Oji-sama, nn！ Nn ah...！ Ah！ Ah！ Auu！ Already...
-already！」</t>
+          <t>「Ah... Oji-sama, nn！ Nn ah...！ Ah！ Ah！ Auu！
+Already... already！」</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8662,8 +8667,8 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>Realizing I was almost at my peak, I clenched my teeth
-to brace for the inevitable moment.</t>
+          <t>Realizing I was almost at my peak, I clenched my
+teeth to brace for the inevitable moment.</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -8893,8 +8898,8 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>At the same time, the vaginal flesh began to writhe as
-if craving semen.</t>
+          <t>At the same time, the vaginal flesh began to writhe
+as if craving semen.</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -9183,8 +9188,8 @@
       <c r="B569" s="1" t="inlineStr">
         <is>
           <t>Meanwhile, sexual juices were slowly oozing out from
-between my legs with a soft squelch, spreading a stain
-across the futon.</t>
+between my legs with a soft squelch, spreading a
+stain across the futon.</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -9655,8 +9660,8 @@
       </c>
       <c r="B600" s="1" t="inlineStr">
         <is>
-          <t>They made me sit seiza, and an interrogation worthy of
-Kikuchiyo-baa-chan began...</t>
+          <t>They made me sit seiza, and an interrogation worthy
+of Kikuchiyo-baa-chan began...</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -9704,9 +9709,9 @@
       </c>
       <c r="B603" s="1" t="inlineStr">
         <is>
-          <t>「...I'll reluctantly accept 'misunderstanding' for the
-sake of argument... at a time like that, well... there
-are ambiguous words that could be said...」</t>
+          <t>「...I'll reluctantly accept 'misunderstanding' for
+the sake of argument... at a time like that, well...
+there are ambiguous words that could be said...」</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -9875,8 +9880,8 @@
       </c>
       <c r="B614" s="1" t="inlineStr">
         <is>
-          <t>「Uh, well, that was wordplay... I just said it sounded
-like she was awake...」</t>
+          <t>「Uh, well, that was wordplay... I just said it
+sounded like she was awake...」</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -9967,8 +9972,8 @@
       </c>
       <c r="B620" s="1" t="inlineStr">
         <is>
-          <t>A cornered feeling—like bad excuses won't work—made me
-shrink back in fear.</t>
+          <t>A cornered feeling—like bad excuses won't work—made
+me shrink back in fear.</t>
         </is>
       </c>
       <c r="C620" t="n">
@@ -10138,8 +10143,8 @@
       <c r="B631" s="1" t="inlineStr">
         <is>
           <t>I'm sorry for waking you, but more than that your
-anger at me is stronger, and you don't have your usual
-gentleness.</t>
+anger at me is stronger, and you don't have your
+usual gentleness.</t>
         </is>
       </c>
       <c r="C631" t="n">
@@ -10231,8 +10236,8 @@
       </c>
       <c r="B637" s="1" t="inlineStr">
         <is>
-          <t>When Rin-chan spotted my posture and laughed shrewdly,
-Miru-chan noticed and started laughing too.</t>
+          <t>When Rin-chan spotted my posture and laughed
+shrewdly, Miru-chan noticed and started laughing too.</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -10431,7 +10436,8 @@
       </c>
       <c r="B650" s="1" t="inlineStr">
         <is>
-          <t>「...But this and that are separate matters, you know？」</t>
+          <t>「...But this and that are separate matters, you
+know？」</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -10476,8 +10482,8 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>At Rurichiyo-chan's beaming smile, I felt a shiver all
-over again.</t>
+          <t>At Rurichiyo-chan's beaming smile, I felt a shiver
+all over again.</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -10507,8 +10513,8 @@
       </c>
       <c r="B655" s="1" t="inlineStr">
         <is>
-          <t>「Hey MiruMiru... maybe Rin and the others should go to
-sleep？」</t>
+          <t>「Hey MiruMiru... maybe Rin and the others should go
+to sleep？」</t>
         </is>
       </c>
       <c r="C655" t="n">

--- a/processed_ruby_restored_xlsx/sc225_瑠璃７：天体観測.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc225_瑠璃７：天体観測.ss.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>She's definitely asleep, isn't she...？</t>
+          <t>She's definitely asleep, isn't she...？"</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>「Nn…!」</t>
+          <t>Nn…!</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>「Nnu… n'! n'! nnu…」</t>
+          <t>Nnu… n'! n'! nnu…</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1109,8 +1109,8 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>「Heh… wriggling your hips in your sleep…
-Rurichiyo-chan is so cute…」</t>
+          <t>Heh… wriggling your hips in your sleep…
+Rurichiyo-chan is so cute…</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>「Nnu… n~u…」</t>
+          <t>Nnu… n~u…</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>「Nn… oops！」</t>
+          <t>Nn… oops！</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ O-ji, sa-maa… suu, suu…」</t>
+          <t>Nn！ O-ji, sa-maa… suu, suu…</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chan… your panties might show, y'know？」</t>
+          <t>Rurichiyo-chan… your panties might show, y'know？</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>「Nnu, nn… suu… fuu, no… desuaa…」</t>
+          <t>Nnu, nn… suu… fuu, no… desuaa…</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>「Suu… suu… n, hafu, fuu… n, nnu！ Faa… fau… n'…」</t>
+          <t>Suu… suu… n, hafu, fuu… n, nnu！ Faa… fau… n'…</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>「Nn… nnu, nnu~…」</t>
+          <t>Nn… nnu, nnu~…</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1492,8 +1492,8 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh, huh！ Th-there... ooh... mmm, nff...！ Ssss...
-*huff*...」</t>
+          <t>Nnngh, huh！ Th-there... ooh... mmm, nff...！ Ssss...
+*huff*...</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1585,8 +1585,8 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>「Rurichiyo-chan, you're actually kind of naughty,
-aren't you...？」</t>
+          <t>Rurichiyo-chan, you're actually kind of naughty,
+aren't you...？</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2012,9 +2012,9 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>She went along with what I said and kept quiet, but
-if I’m right there when she wakes up, of course she’s
-going to be curious...</t>
+          <t>I let her steer the conversation and fell silent, but
+if I’m sitting in front of her when she wakes up, of
+course she's going to be curious...</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2153,8 +2153,8 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>「Well, I don't think you need to worry about it that
-much.」</t>
+          <t>Well, I don't think you need to worry about it that
+much.</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... you're getting hot, aren't you...？」</t>
+          <t>Mmm... you're getting hot, aren't you...？</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>「Ah… I'm the one who can't take it anymore… see？」</t>
+          <t>Ah… I'm the one who can't take it anymore… see？</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan twisted around to face me and,
+          <t>Rurichiyo-chan twisted around to face him and,
 spotting the penis, her eyes went wide.</t>
         </is>
       </c>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>「Nn... ah, ah！」</t>
+          <t>Nn... ah, ah！</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5327,8 +5327,8 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>I lift Rurichiyo-chan’s slim legs and push my penis
-in.</t>
+          <t>He lifts Rurichiyo-chan’s slim legs and pushes his
+penis in.</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh... ah, aahh...！ Oji-sama...」</t>
+          <t>Nnngh... ah, aahh...！ Oji-sama...</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t>「Haa... haa~~~...」</t>
+          <t>Haa... haa~~~...</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t>「An！？ Aah... Oji-sama... aaah！」</t>
+          <t>An！？ Aah... Oji-sama... aaah！</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>「Wah！ Rurichiyo-chan, your voice！ Voic...！」</t>
+          <t>Wah！ Rurichiyo-chan, your voice！ Voic...！</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>「Nn！？ Nn, nnh... ... ffu, fuu... nn, nn...」</t>
+          <t>Nn！？ Nn, nnh... ... ffu, fuu... nn, nn...</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -6323,8 +6323,8 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>「Huu, fufuu... Ah, ha！ That's not what I meant— Aha,
-haa...！」</t>
+          <t>Huu, fufuu... Ah, ha！ That's not what I meant— Aha,
+haa...！</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>I feel it buried deep inside her pussy, like it's
+          <t>I feel it buried deep inside my pussy, like it's
 completely wrapped from the base all the way to the
 tip….</t>
         </is>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t>The tip that had been prodding the depths of her
+          <t>The tip that had been prodding the depths of my
 vagina is softly crushed.</t>
         </is>
       </c>
@@ -7006,8 +7006,8 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>「Ahh... Rurichiyo-chan, you're wetter than usual...
-it's all squelchy...！」</t>
+          <t>Ahh... Rurichiyo-chan, you're wetter than usual...
+it's all squelchy...！</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t>「Fwaaah...！ Nn...！ Nfuu...！ Nn, nn...！」</t>
+          <t>Fwaaah...！ Nn...！ Nfuu...！ Nn, nn...！</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -7083,8 +7083,8 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t>「Ahh... because Rurichiyo-chan's trying so hard... it
-feels good for me too...！」</t>
+          <t>Ahh... because Rurichiyo-chan's trying so hard... it
+feels good for me too...！</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="B434" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama~... uu, nmmuu...！」</t>
+          <t>Oji-sama~... uu, nmmuu...！</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t>「...You're so good, holding it in properly, huh？」</t>
+          <t>...You're so good, holding it in properly, huh？</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -7236,8 +7236,8 @@
       </c>
       <c r="B442" s="1" t="inlineStr">
         <is>
-          <t>「Fuh, fuh—ah, nn！ Gotta hold it… nnnah！ Nnaaah…
-gotta, nnaa… haaah…」</t>
+          <t>Fuh, fuh—ah, nn！ Gotta hold it… nnnah！ Nnaaah… gotta,
+nnaa… haaah…</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="B447" s="1" t="inlineStr">
         <is>
-          <t>「Hah, haa... does it feel... good？」</t>
+          <t>Hah, haa... does it feel... good？</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -7557,8 +7557,8 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>The sudden stimulation must have caught her off
-guard, and Rurichiyo-chan let out an airy cry.</t>
+          <t>It seemed to be an unexpected刺激, and Rurichiyo-chan
+let out a loose, surprised cry.</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="B503" s="1" t="inlineStr">
         <is>
-          <t>「Phew, hufff…！ Hah, nna…！」</t>
+          <t>Phew, hufff…！ Hah, nna…！</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>It's tightening up around her pussy again…！？</t>
+          <t>It's tightening up around my pussy again…！？</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t>「Haa... fuu, ah！ Oji-sama... n'uaaah...」</t>
+          <t>Haa... fuu, ah！ Oji-sama... n'uaaah...</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>When my penis throbbed violently, her pussy answered
+          <t>When his penis throbbed violently, her pussy answered
 in kind, making the soft inner walls ripple and come
 alive.</t>
         </is>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="B512" s="1" t="inlineStr">
         <is>
-          <t>「Ah… me, me！ I can't hold back anymore…！」</t>
+          <t>Ah… me, me！ I can't hold back anymore…！</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B514" s="1" t="inlineStr">
         <is>
-          <t>「Uaa… I c-can't… Oji-sama, ah…！」</t>
+          <t>Uaa… I c-can't… Oji-sama, ah…！</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -8406,7 +8406,7 @@
       <c r="B518" s="1" t="inlineStr">
         <is>
           <t>I can feel we're joined at the very deepest place,
-and my penis shudders in delight.</t>
+and his penis shudders in delight.</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8452,8 +8452,8 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>「Nn-ah! melting... phew! I'm gonna lose it... nn-ah!
-already, already—ah! Nnngh~~!」</t>
+          <t>Nn-ah! melting... phew! I'm gonna lose it... nn-ah!
+already, already—ah! Nnngh~~!</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="B532" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="B533" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Ah...uk！ Huu, uuu...！ Nn, nn, nn, nn, nn！ Aah！」</t>
+          <t>Nn！ Ah...uk！ Huu, uuu...！ Nn, nn, nn, nn, nn！ Aah！</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -8744,7 +8744,7 @@
       <c r="B540" s="1" t="inlineStr">
         <is>
           <t>With the resonant voice, Rurichiyo-chan’s vagina
-tightens around me.</t>
+tightens around him.</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>「Aahnnngh！ Nngh！ Uuuaaahh, nnn！」</t>
+          <t>Aahnnngh！ Nngh！ Uuuaaahh, nnn！</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="B563" s="1" t="inlineStr">
         <is>
-          <t>My hips sagged, and my penis slipped out...</t>
+          <t>My hips sagged, and his penis slipped out...</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -10220,8 +10220,8 @@
       </c>
       <c r="B636" s="1" t="inlineStr">
         <is>
-          <t>「Pff！ Aha, ahaha！ Onii-chan, what's wrong？ Are you
-being scolded？」</t>
+          <t>Pff！ Aha, ahaha！ Onii-chan, what's wrong？ Are you
+being scolded？</t>
         </is>
       </c>
       <c r="C636" t="n">
@@ -10405,8 +10405,8 @@
       <c r="B648" s="1" t="inlineStr">
         <is>
           <t>Miru-chan and Rin-chan laughed uproariously while
-Nono-chan wouldn't wake up… even I couldn't help but
-give a wry smile at that.</t>
+Monono-chan wouldn't wake up… even I couldn't help
+but give a wry smile at that.</t>
         </is>
       </c>
       <c r="C648" t="n">
